--- a/StructureDefinition-ophthalmic-device.xlsx
+++ b/StructureDefinition-ophthalmic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T20:04:06+00:00</t>
+    <t>2026-08-19T17:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-device.xlsx
+++ b/StructureDefinition-ophthalmic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:13:42+00:00</t>
+    <t>2026-08-19T17:55:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-device.xlsx
+++ b/StructureDefinition-ophthalmic-device.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T17:55:33+00:00</t>
+    <t>2026-08-25T00:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-device.xlsx
+++ b/StructureDefinition-ophthalmic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T00:41:24+00:00</t>
+    <t>2026-08-25T02:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-device.xlsx
+++ b/StructureDefinition-ophthalmic-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T02:25:39+00:00</t>
+    <t>2026-08-25T18:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-device.xlsx
+++ b/StructureDefinition-ophthalmic-device.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T18:52:20+00:00</t>
+    <t>2026-09-01T17:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
